--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="133">
   <si>
     <t>Allocation</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Mazhar School</t>
   </si>
   <si>
-    <t>UAT Done, Sign off shared with Paysys and OPG team for implementaiton. Circular pending</t>
-  </si>
-  <si>
     <t>NTC - National Telecommunication Centre</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>Bhawan</t>
   </si>
   <si>
-    <t>Court Management  System</t>
-  </si>
-  <si>
     <t>UAT has been done, currently under IS review</t>
   </si>
   <si>
@@ -140,12 +134,6 @@
     <t>Payment</t>
   </si>
   <si>
-    <t>RAAST / RTGS Enhencement - DMS</t>
-  </si>
-  <si>
-    <t>UAT Done, CMC Approved, Deployment done</t>
-  </si>
-  <si>
     <t>PSW</t>
   </si>
   <si>
@@ -179,18 +167,9 @@
     <t>Bulk SIDA Upload Limit 50 K</t>
   </si>
   <si>
-    <t>SOW and FSD Finalized, UAT Done, Under IS review</t>
-  </si>
-  <si>
     <t>Resent of Title Fetch - SmartPAY</t>
   </si>
   <si>
-    <t>BRD rasied, SOW finalizated. FSD Finalized, Effort approved, UAT Done, Under IS review</t>
-  </si>
-  <si>
-    <t>In Process</t>
-  </si>
-  <si>
     <t>Status Update SmartPAY</t>
   </si>
   <si>
@@ -200,9 +179,6 @@
     <t>UBCS</t>
   </si>
   <si>
-    <t>Balance Inquiry Limit</t>
-  </si>
-  <si>
     <t>SOW finalized, FSD revised required. UAT done, Production deployment done</t>
   </si>
   <si>
@@ -221,27 +197,15 @@
     <t>Under Scoping</t>
   </si>
   <si>
-    <t>Banker Cheque issuance and collection via CRPL</t>
-  </si>
-  <si>
     <t>BRD shared with IT.</t>
   </si>
   <si>
     <t>Outward Clearing</t>
   </si>
   <si>
-    <t>Under UAT, Issue at CORE end</t>
-  </si>
-  <si>
     <t>SIEM Intergration</t>
   </si>
   <si>
-    <t>Under UAT, Observation raised with CRPL, Meeting requested with IT PMO</t>
-  </si>
-  <si>
-    <t>SIT</t>
-  </si>
-  <si>
     <t>SWAP</t>
   </si>
   <si>
@@ -251,18 +215,12 @@
     <t>CNIC Screening -ATA</t>
   </si>
   <si>
-    <t>UAT DONE by DBG, Complaince UAT in process.</t>
-  </si>
-  <si>
     <t>Discontinuation of SOAP to REST</t>
   </si>
   <si>
     <t>1Link document shared, Paysys document received, SIT DONE, UAT DONE, CMC Approved</t>
   </si>
   <si>
-    <t>E-Stamping Sindh (Addition of property tax)</t>
-  </si>
-  <si>
     <t>API document received, meeting will be scheduled for kick off, Test Transaction performed and shared for validation, UAT DONE.</t>
   </si>
   <si>
@@ -275,9 +233,6 @@
     <t>Tokinization on SmartPAY</t>
   </si>
   <si>
-    <t>IS issue. UAT DONE for UBCS, RAAST, IBFT, CMC approved</t>
-  </si>
-  <si>
     <t>Under Development</t>
   </si>
   <si>
@@ -287,21 +242,12 @@
     <t>Requirement shared with CRPL, SOW finalizaed, FSD finalized, under development</t>
   </si>
   <si>
-    <t>Control Gap in Bulk Processing – MCA</t>
-  </si>
-  <si>
     <t>Encryption of Bulk Account upload</t>
   </si>
   <si>
     <t>SOW finalized, FSD received . AES encrption required</t>
   </si>
   <si>
-    <t>Collection of Dealer via Mobile APP</t>
-  </si>
-  <si>
-    <t>BRD raised with Aroosa</t>
-  </si>
-  <si>
     <t>File upload via Email</t>
   </si>
   <si>
@@ -332,12 +278,6 @@
     <t>Revised FSd required from CRPL</t>
   </si>
   <si>
-    <t>Purpose code required in IBT</t>
-  </si>
-  <si>
-    <t>BRD raised with ITG</t>
-  </si>
-  <si>
     <t>Adnan Younis</t>
   </si>
   <si>
@@ -371,9 +311,6 @@
     <t xml:space="preserve">AI Automation </t>
   </si>
   <si>
-    <t>AI-Driven Automation: Enhancing Operational Efficiency</t>
-  </si>
-  <si>
     <t>Our team is currently developing AI automation solutions to enhance operational efficiency.</t>
   </si>
   <si>
@@ -396,6 +333,96 @@
   </si>
   <si>
     <t>Saad Asif</t>
+  </si>
+  <si>
+    <t>UAT Done,  Circular pending</t>
+  </si>
+  <si>
+    <t>UAT Done, Circular pending</t>
+  </si>
+  <si>
+    <t>Court Management System</t>
+  </si>
+  <si>
+    <t>Under Is review.</t>
+  </si>
+  <si>
+    <t>SOW finalized, FSD received, Under UAT, Under Is review.</t>
+  </si>
+  <si>
+    <t>SOW finalized, FSD received, Under UAT,Under Is review.</t>
+  </si>
+  <si>
+    <t>Collection of Dealer via App</t>
+  </si>
+  <si>
+    <t>Host to Host Integration</t>
+  </si>
+  <si>
+    <t>Purpose Code</t>
+  </si>
+  <si>
+    <t>Balance Inquiry Length Enhancement</t>
+  </si>
+  <si>
+    <t>QR Upload</t>
+  </si>
+  <si>
+    <t>SME Onboarding</t>
+  </si>
+  <si>
+    <t>RAAST/RTGS DMS</t>
+  </si>
+  <si>
+    <t>Live.</t>
+  </si>
+  <si>
+    <t>Under Scoping.</t>
+  </si>
+  <si>
+    <t>BRD shared.</t>
+  </si>
+  <si>
+    <t>Production deployment done</t>
+  </si>
+  <si>
+    <t>Banker Cheque collection via CRPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Gap in Bulk Processing </t>
+  </si>
+  <si>
+    <t>E-Stamping (Addition of property tax)</t>
+  </si>
+  <si>
+    <t>DBG UAT Done,Under UAT at OPG and Core end</t>
+  </si>
+  <si>
+    <t>Under UAT, Observation raised with CRPL, IS requested for logs.</t>
+  </si>
+  <si>
+    <t>UAT DONE by DBG, Live.</t>
+  </si>
+  <si>
+    <t>IS issue. UAT DONE for UBCS, RAAST, IBFT, CMC approved,Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasa Lahore </t>
+  </si>
+  <si>
+    <t>WASA Faisalabad</t>
+  </si>
+  <si>
+    <t>FESCO</t>
+  </si>
+  <si>
+    <t>UGDCL</t>
+  </si>
+  <si>
+    <t>AI-Driven Automation</t>
+  </si>
+  <si>
+    <t>CMC</t>
   </si>
 </sst>
 </file>
@@ -419,7 +446,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,12 +467,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -458,18 +479,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -577,11 +598,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -595,32 +627,36 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,8 +925,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F49" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F56" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F56"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1166,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -1178,27 +1214,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1211,12 +1247,12 @@
         <v>9</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="25" t="s">
-        <v>10</v>
+      <c r="F2" s="17" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1229,880 +1265,1011 @@
         <v>11</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="25" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="25" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="25" t="s">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="25" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="25" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E9" s="3">
         <v>46218</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E10" s="3">
         <v>46218</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E11" s="3">
         <v>46220</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E12" s="3">
         <v>46176</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="5" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="26" t="s">
+      <c r="E14" s="37"/>
+      <c r="F14" s="38" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="37">
+        <v>46125</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="37"/>
+      <c r="F16" s="38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="C19" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="37">
+        <v>46227</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="6">
+        <v>46161</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="6">
+        <v>46147</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="6">
+        <v>46122</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="9">
+        <v>46059</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="9">
+        <v>46181</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="9">
+        <v>46227</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="9">
+        <v>46161</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="9">
+        <v>46181</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="37"/>
+      <c r="F40" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="6">
         <v>46125</v>
       </c>
-      <c r="F15" s="26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="F41" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="6">
-        <v>46227</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="27" t="s">
+      <c r="B42" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="9">
-        <v>46161</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="9">
-        <v>46147</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="9">
-        <v>46122</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="12">
-        <v>46059</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="11" t="s">
+      <c r="D42" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="12">
-        <v>46181</v>
-      </c>
-      <c r="F31" s="28" t="s">
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="12">
-        <v>46227</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="10" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="37"/>
+      <c r="F43" s="38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="B44" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="28" t="s">
+      <c r="C44" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="E44" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="12">
-        <v>46161</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="11" t="s">
+      <c r="B45" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="28" t="s">
+      <c r="F45" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" s="11" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="28" t="s">
+      <c r="B47" s="10" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="C47" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="28" t="s">
+      <c r="C48" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="26" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="12">
-        <v>46181</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="29" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="16" t="s">
+      <c r="E48" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" s="17" t="s">
+      <c r="E49" s="32"/>
+      <c r="F49" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E45" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F45" s="30" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="16" t="s">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" s="30" t="s">
+      <c r="E52" s="6">
+        <v>46220</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="31" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" s="16" t="s">
+      <c r="E53" s="32"/>
+      <c r="F53" s="33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48" s="16" t="s">
+      <c r="E54" s="32"/>
+      <c r="F54" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F48" s="30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>122</v>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="E55" s="41"/>
+      <c r="F55" s="42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="41"/>
+      <c r="F56" s="42" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="136">
   <si>
     <t>Allocation</t>
   </si>
@@ -423,13 +423,22 @@
   </si>
   <si>
     <t>CMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment </t>
+  </si>
+  <si>
+    <t>Virtual Account for supporting SIDA</t>
+  </si>
+  <si>
+    <t>Discussion going on between SOW DBG and CRPL.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +452,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -613,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -657,6 +673,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -925,8 +946,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F56" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F57" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F57"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1202,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -2265,6 +2286,24 @@
         <v>56</v>
       </c>
     </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="46"/>
+      <c r="F57" s="47" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="140">
   <si>
     <t>Allocation</t>
   </si>
@@ -432,6 +432,18 @@
   </si>
   <si>
     <t>Discussion going on between SOW DBG and CRPL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin </t>
+  </si>
+  <si>
+    <t>Admin MGMT</t>
+  </si>
+  <si>
+    <t>UAT Done.</t>
+  </si>
+  <si>
+    <t>E Stamping Sindh</t>
   </si>
 </sst>
 </file>
@@ -462,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +514,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -678,6 +696,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -946,8 +974,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F57" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F59" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F59"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1223,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -1441,22 +1469,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="51">
         <v>46176</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="52" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2302,6 +2330,42 @@
       <c r="E57" s="46"/>
       <c r="F57" s="47" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" s="56"/>
+      <c r="F58" s="57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="56"/>
+      <c r="F59" s="57" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1429,99 +1429,99 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E12" s="3">
         <v>46218</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F12" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E13" s="3">
         <v>46220</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F13" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="48" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="49" t="s">
+      <c r="B14" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D14" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E14" s="51">
         <v>46176</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F14" s="52" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1532,16 +1532,14 @@
         <v>7</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="37">
-        <v>46125</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E15" s="37"/>
       <c r="F15" s="38" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1549,17 +1547,17 @@
         <v>31</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1567,17 +1565,19 @@
         <v>31</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="37"/>
+        <v>127</v>
+      </c>
+      <c r="E17" s="37">
+        <v>46125</v>
+      </c>
       <c r="F17" s="38" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1588,784 +1588,784 @@
         <v>36</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="38" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="37"/>
+      <c r="F21" s="38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="37"/>
+      <c r="F22" s="38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="37"/>
+      <c r="F24" s="38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C25" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D25" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E25" s="37">
         <v>46227</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="F25" s="38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B26" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="6">
+        <v>46125</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="6">
+        <v>46220</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="32"/>
+      <c r="F33" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="s">
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="s">
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="s">
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E37" s="6">
         <v>46161</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F37" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E38" s="6">
         <v>46147</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F38" s="18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E39" s="6">
         <v>46122</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F39" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="19" t="s">
+      <c r="E40" s="9"/>
+      <c r="F40" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D41" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="19" t="s">
+      <c r="E41" s="9"/>
+      <c r="F41" s="19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B42" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D42" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="19" t="s">
+      <c r="E42" s="9"/>
+      <c r="F42" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="19" t="s">
+      <c r="E43" s="9"/>
+      <c r="F43" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="B44" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E44" s="9">
         <v>46059</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F44" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B45" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D45" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E45" s="9">
         <v>46181</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F45" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="B46" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D46" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E46" s="9">
         <v>46227</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F46" s="19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B47" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="19" t="s">
+      <c r="E47" s="9"/>
+      <c r="F47" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="19" t="s">
+      <c r="E48" s="9"/>
+      <c r="F48" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D49" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E49" s="9">
         <v>46161</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F49" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B50" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D50" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="19" t="s">
+      <c r="E50" s="9"/>
+      <c r="F50" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="19" t="s">
+      <c r="E51" s="9"/>
+      <c r="F51" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="B52" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="19" t="s">
+      <c r="E52" s="9"/>
+      <c r="F52" s="19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B53" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E53" s="9">
         <v>46181</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F53" s="19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="37"/>
-      <c r="F40" s="38" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="6">
-        <v>46125</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="4" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="35" t="s">
+      <c r="D54" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="E54" s="46"/>
+      <c r="F54" s="47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="D55" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+      <c r="B56" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="10" t="s">
+      <c r="B57" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="12" t="s">
+      <c r="D57" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F45" s="20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="F57" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" s="12" t="s">
+      <c r="D58" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F46" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="F58" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="10" t="s">
+      <c r="B59" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="12" t="s">
+      <c r="D59" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F47" s="20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" s="26" t="s">
+      <c r="F59" s="28" t="s">
         <v>101</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" s="32"/>
-      <c r="F49" s="33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E52" s="6">
-        <v>46220</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="E53" s="32"/>
-      <c r="F53" s="33" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B56" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="C57" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D57" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" s="56"/>
-      <c r="F58" s="57" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" s="56"/>
-      <c r="F59" s="57" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="148">
   <si>
     <t>Allocation</t>
   </si>
@@ -77,12 +77,6 @@
     <t>IS Review</t>
   </si>
   <si>
-    <t>PASSPOST FEE MIS reporting and QR</t>
-  </si>
-  <si>
-    <t>SOW finalizated, FSD received, UAT Done. Production deployment and implenentaiton required, Under IS review</t>
-  </si>
-  <si>
     <t>University of Balistan Skardu</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>Bhawan</t>
   </si>
   <si>
-    <t>UAT has been done, currently under IS review</t>
-  </si>
-  <si>
     <t>LESCO</t>
   </si>
   <si>
@@ -347,21 +338,9 @@
     <t>Under Is review.</t>
   </si>
   <si>
-    <t>SOW finalized, FSD received, Under UAT, Under Is review.</t>
-  </si>
-  <si>
-    <t>SOW finalized, FSD received, Under UAT,Under Is review.</t>
-  </si>
-  <si>
     <t>Collection of Dealer via App</t>
   </si>
   <si>
-    <t>Host to Host Integration</t>
-  </si>
-  <si>
-    <t>Purpose Code</t>
-  </si>
-  <si>
     <t>Balance Inquiry Length Enhancement</t>
   </si>
   <si>
@@ -383,9 +362,6 @@
     <t>BRD shared.</t>
   </si>
   <si>
-    <t>Production deployment done</t>
-  </si>
-  <si>
     <t>Banker Cheque collection via CRPL</t>
   </si>
   <si>
@@ -407,12 +383,6 @@
     <t>IS issue. UAT DONE for UBCS, RAAST, IBFT, CMC approved,Live</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasa Lahore </t>
-  </si>
-  <si>
-    <t>WASA Faisalabad</t>
-  </si>
-  <si>
     <t>FESCO</t>
   </si>
   <si>
@@ -444,6 +414,60 @@
   </si>
   <si>
     <t>E Stamping Sindh</t>
+  </si>
+  <si>
+    <t>BRD shared. Pending from Paysys and Mobile App team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raast OTC - Auto Reversal </t>
+  </si>
+  <si>
+    <t>Paysys has not developed Raast OTC auto reversal scenario while it was tested by Tayyab bhai.</t>
+  </si>
+  <si>
+    <t>Single Check Multiple Bills</t>
+  </si>
+  <si>
+    <t>PASSPORT FEE MIS reporting and QR</t>
+  </si>
+  <si>
+    <t>SOW finalizated, FSD received, UAT Done. Production deployment and implenentaiton required, Under IS review, At CMC</t>
+  </si>
+  <si>
+    <t>WASA Faisalabad (Offline Biller)</t>
+  </si>
+  <si>
+    <t>UAT has been done, circular pending.</t>
+  </si>
+  <si>
+    <t>Wasa Lahore (API)</t>
+  </si>
+  <si>
+    <t>UAT DONE, Branch mapping and Mis reports pending at crpl.</t>
+  </si>
+  <si>
+    <t>Under development</t>
+  </si>
+  <si>
+    <t>Purpose of payment in CORE naarration (IBT)</t>
+  </si>
+  <si>
+    <t>Under developmet</t>
+  </si>
+  <si>
+    <t>SOW finalized, FSD received, Under UAT,Under Is review. For CMC approval</t>
+  </si>
+  <si>
+    <t>VM Transafer</t>
+  </si>
+  <si>
+    <t>AT IT end.</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -474,7 +498,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,19 +531,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,59 +688,84 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -724,38 +779,17 @@
         </left>
         <right/>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -773,13 +807,17 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -812,13 +850,17 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -851,13 +893,17 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -888,13 +934,17 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
           <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -949,7 +999,7 @@
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -958,6 +1008,12 @@
         </right>
         <top/>
         <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -974,15 +1030,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F59" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F61" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F61"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
     <tableColumn id="3" name="Status " dataDxfId="3"/>
     <tableColumn id="4" name="Mandate" dataDxfId="2"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
-    <tableColumn id="6" name="Update" dataDxfId="0"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="0"/>
+    <tableColumn id="6" name="Update" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1251,39 +1307,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="57" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1295,13 +1351,15 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="17" t="s">
-        <v>104</v>
+      <c r="E2" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1313,1059 +1371,1171 @@
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="17" t="s">
-        <v>103</v>
+      <c r="E3" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="17" t="s">
+      <c r="E5" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="17" t="s">
+      <c r="E7" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="17" t="s">
+      <c r="E8" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="17" t="s">
+      <c r="D9" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E9" s="3">
         <v>46218</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="9">
+        <v>46218</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B13" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="9">
+        <v>46220</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="9">
+        <v>46176</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="E17" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="57" t="s">
+      <c r="D18" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="48" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="55" t="s">
+      <c r="E19" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="49">
+        <v>46241</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="57" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46218</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46220</v>
-      </c>
-      <c r="F13" s="17" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="51">
-        <v>46176</v>
-      </c>
-      <c r="F14" s="52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="35" t="s">
+      <c r="B22" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="37"/>
-      <c r="F15" s="38" t="s">
+      <c r="D22" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="47" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="37"/>
-      <c r="F16" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="37">
+      <c r="C24" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="49">
+        <v>46227</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="6">
         <v>46125</v>
       </c>
-      <c r="F17" s="38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="35" t="s">
+      <c r="F27" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="38" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38" t="s">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38" t="s">
+      <c r="B30" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="36" t="s">
+      <c r="E31" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="37">
-        <v>46227</v>
-      </c>
-      <c r="F25" s="38" t="s">
+      <c r="E34" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" s="6">
-        <v>46125</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="6">
-        <v>46220</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="33" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="s">
-        <v>107</v>
+      <c r="E35" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>45</v>
+      <c r="A36" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>45</v>
+      <c r="A37" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E37" s="6">
         <v>46161</v>
       </c>
-      <c r="F37" s="18" t="s">
-        <v>51</v>
+      <c r="F37" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>45</v>
+      <c r="A38" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E38" s="6">
         <v>46147</v>
       </c>
-      <c r="F38" s="18" t="s">
-        <v>53</v>
+      <c r="F38" s="14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>45</v>
+      <c r="A39" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E39" s="6">
         <v>46122</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="7" t="s">
+      <c r="E40" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="19" t="s">
+      <c r="E41" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="7" t="s">
+      <c r="E42" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="9">
+        <v>46059</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="9">
+        <v>46181</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E45" s="9">
+        <v>46227</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="9">
+        <v>46161</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" s="9">
+        <v>46181</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" s="54" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F56" s="45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="9">
-        <v>46059</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="9">
-        <v>46181</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" s="9">
-        <v>46227</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="9">
-        <v>46161</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="9">
-        <v>46181</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="E54" s="46"/>
-      <c r="F54" s="47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F59" s="28" t="s">
-        <v>101</v>
+      <c r="D60" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F60" s="45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -677,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -738,34 +738,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -790,6 +771,29 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1037,8 +1041,8 @@
     <tableColumn id="2" name="Category" dataDxfId="4"/>
     <tableColumn id="3" name="Status " dataDxfId="3"/>
     <tableColumn id="4" name="Mandate" dataDxfId="2"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="0"/>
-    <tableColumn id="6" name="Update" dataDxfId="1"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
+    <tableColumn id="6" name="Update" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1598,64 +1602,64 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>140</v>
+      <c r="D15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="33" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E17" s="9">
         <v>46176</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F17" s="15" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1669,13 +1673,13 @@
         <v>8</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="E18" s="56" t="s">
         <v>147</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1689,13 +1693,13 @@
         <v>8</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="E19" s="56" t="s">
         <v>147</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,59 +1707,59 @@
         <v>29</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="49">
-        <v>46241</v>
+        <v>138</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>147</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="51" t="s">
-        <v>7</v>
+      <c r="B21" s="47" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>139</v>
+        <v>21</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="49">
+        <v>46241</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="47" t="s">
-        <v>33</v>
+      <c r="B22" s="51" t="s">
+        <v>7</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>119</v>
       </c>
       <c r="E22" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="F22" s="50" t="s">
-        <v>37</v>
+      <c r="F22" s="53" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1763,19 +1767,19 @@
         <v>29</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E23" s="56" t="s">
         <v>147</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2318,7 +2322,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>99</v>
       </c>
@@ -2338,7 +2342,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>99</v>
       </c>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -239,9 +239,6 @@
     <t>SOW finalized, FSD received . AES encrption required</t>
   </si>
   <si>
-    <t>File upload via Email</t>
-  </si>
-  <si>
     <t>BRD raised with CRPL, SOW finalized, FSD and efforts required</t>
   </si>
   <si>
@@ -287,9 +284,6 @@
     <t>Vendor Payments</t>
   </si>
   <si>
-    <t xml:space="preserve">In Process </t>
-  </si>
-  <si>
     <t>Pay orders dispatched to CRPL.</t>
   </si>
   <si>
@@ -468,6 +462,12 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File upload via Email /SFTP </t>
   </si>
 </sst>
 </file>
@@ -1356,10 +1356,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,10 +1376,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1396,7 +1396,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>13</v>
@@ -1416,7 +1416,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>15</v>
@@ -1430,16 +1430,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,7 +1456,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>18</v>
@@ -1476,7 +1476,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>20</v>
@@ -1507,19 +1507,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1533,13 +1533,13 @@
         <v>21</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1573,13 +1573,13 @@
         <v>21</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1616,7 +1616,7 @@
         <v>69</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>70</v>
@@ -1633,13 +1633,13 @@
         <v>66</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1673,13 +1673,13 @@
         <v>8</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,7 +1696,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F19" s="50" t="s">
         <v>31</v>
@@ -1713,10 +1713,10 @@
         <v>8</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F20" s="50" t="s">
         <v>10</v>
@@ -1753,13 +1753,13 @@
         <v>8</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,7 +1776,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F23" s="50" t="s">
         <v>37</v>
@@ -1813,13 +1813,13 @@
         <v>16</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E25" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1833,13 +1833,13 @@
         <v>53</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E26" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1853,13 +1853,13 @@
         <v>21</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E27" s="6">
         <v>46125</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1873,13 +1873,13 @@
         <v>66</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1893,13 +1893,13 @@
         <v>66</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,19 +1907,19 @@
         <v>42</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>66</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1933,13 +1933,13 @@
         <v>53</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="E31" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1953,13 +1953,13 @@
         <v>53</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1973,13 +1973,13 @@
         <v>53</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1990,16 +1990,16 @@
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E34" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2010,16 +2010,16 @@
         <v>32</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>45</v>
       </c>
       <c r="E36" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>46</v>
@@ -2053,7 +2053,7 @@
         <v>21</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" s="6">
         <v>46161</v>
@@ -2104,7 +2104,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>7</v>
@@ -2116,15 +2116,15 @@
         <v>55</v>
       </c>
       <c r="E40" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>32</v>
@@ -2136,15 +2136,15 @@
         <v>56</v>
       </c>
       <c r="E41" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>7</v>
@@ -2156,7 +2156,7 @@
         <v>57</v>
       </c>
       <c r="E42" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>58</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>7</v>
@@ -2179,12 +2179,12 @@
         <v>46059</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>47</v>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>7</v>
@@ -2213,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E45" s="9">
         <v>46227</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>47</v>
@@ -2236,7 +2236,7 @@
         <v>67</v>
       </c>
       <c r="E46" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>68</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>47</v>
@@ -2253,10 +2253,10 @@
         <v>66</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E47" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>68</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>32</v>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>32</v>
@@ -2293,18 +2293,18 @@
         <v>66</v>
       </c>
       <c r="D49" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49" s="15" t="s">
         <v>71</v>
-      </c>
-      <c r="E49" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>32</v>
@@ -2313,18 +2313,18 @@
         <v>53</v>
       </c>
       <c r="D50" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F50" s="15" t="s">
         <v>75</v>
-      </c>
-      <c r="E50" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>7</v>
@@ -2333,18 +2333,18 @@
         <v>53</v>
       </c>
       <c r="D51" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>79</v>
-      </c>
-      <c r="E51" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>32</v>
@@ -2359,72 +2359,72 @@
         <v>46181</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C53" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E53" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D54" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="E54" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="54" t="s">
         <v>94</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="E54" s="55" t="s">
-        <v>89</v>
-      </c>
-      <c r="F54" s="54" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C55" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" s="55" t="s">
-        <v>89</v>
-      </c>
       <c r="F55" s="54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>7</v>
@@ -2433,78 +2433,78 @@
         <v>53</v>
       </c>
       <c r="D56" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="45" t="s">
         <v>77</v>
-      </c>
-      <c r="E56" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F56" s="45" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="42" t="s">
         <v>81</v>
-      </c>
-      <c r="B57" s="42" t="s">
-        <v>82</v>
       </c>
       <c r="C57" s="42" t="s">
         <v>53</v>
       </c>
       <c r="D57" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="E57" s="44" t="s">
+      <c r="F57" s="45" t="s">
         <v>84</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B58" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="42" t="s">
+      <c r="E58" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="43" t="s">
+      <c r="F58" s="45" t="s">
         <v>88</v>
-      </c>
-      <c r="E58" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="E59" s="44" t="s">
-        <v>89</v>
-      </c>
       <c r="F59" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" s="42" t="s">
         <v>33</v>
@@ -2516,7 +2516,7 @@
         <v>38</v>
       </c>
       <c r="E60" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F60" s="45" t="s">
         <v>39</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>7</v>
@@ -2533,10 +2533,10 @@
         <v>53</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E61" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F61" s="45" t="s">
         <v>54</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="149">
   <si>
     <t>Allocation</t>
   </si>
@@ -86,9 +86,6 @@
     <t>University of SWAT</t>
   </si>
   <si>
-    <t>API shared with Paysys, Under UAT</t>
-  </si>
-  <si>
     <t>LIVE</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>Optimization</t>
   </si>
   <si>
-    <t>Under Development, CRPL and PAYSYS meeting</t>
-  </si>
-  <si>
     <t>PTCL Advance Payment</t>
   </si>
   <si>
@@ -350,9 +344,6 @@
     <t>Live.</t>
   </si>
   <si>
-    <t>Under Scoping.</t>
-  </si>
-  <si>
     <t>BRD shared.</t>
   </si>
   <si>
@@ -425,9 +416,6 @@
     <t>PASSPORT FEE MIS reporting and QR</t>
   </si>
   <si>
-    <t>SOW finalizated, FSD received, UAT Done. Production deployment and implenentaiton required, Under IS review, At CMC</t>
-  </si>
-  <si>
     <t>WASA Faisalabad (Offline Biller)</t>
   </si>
   <si>
@@ -446,9 +434,6 @@
     <t>Purpose of payment in CORE naarration (IBT)</t>
   </si>
   <si>
-    <t>Under developmet</t>
-  </si>
-  <si>
     <t>SOW finalized, FSD received, Under UAT,Under Is review. For CMC approval</t>
   </si>
   <si>
@@ -468,6 +453,24 @@
   </si>
   <si>
     <t xml:space="preserve">File upload via Email /SFTP </t>
+  </si>
+  <si>
+    <t>SOW finalizated, FSD received, UAT Done. Production deployment and implenentaiton required, Under IS review, CMC approved.</t>
+  </si>
+  <si>
+    <t>API shared with Paysys, UAT Done, circular pending</t>
+  </si>
+  <si>
+    <t>UAT DONE, Circular pending, Live</t>
+  </si>
+  <si>
+    <t>Under scoping, CRPL and PAYSYS meeting done, SOW required</t>
+  </si>
+  <si>
+    <t>Under scoping</t>
+  </si>
+  <si>
+    <t>Under Scoping.BRD Shared with crpl</t>
   </si>
 </sst>
 </file>
@@ -1356,10 +1359,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,10 +1379,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,13 +1393,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>13</v>
@@ -1410,13 +1413,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>15</v>
@@ -1430,16 +1433,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1450,13 +1453,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>18</v>
@@ -1476,10 +1479,10 @@
         <v>19</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1490,16 +1493,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E9" s="3">
         <v>46218</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1507,19 +1510,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E10" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1530,16 +1533,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1550,16 +1553,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="9">
         <v>46218</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1570,16 +1573,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,16 +1593,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="9">
         <v>46220</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.25">
@@ -1610,16 +1613,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1630,16 +1633,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1650,21 +1653,21 @@
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="9">
         <v>46176</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="47" t="s">
         <v>7</v>
@@ -1673,18 +1676,18 @@
         <v>8</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E18" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="47" t="s">
         <v>7</v>
@@ -1693,18 +1696,18 @@
         <v>8</v>
       </c>
       <c r="D19" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="50" t="s">
         <v>30</v>
-      </c>
-      <c r="E19" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F19" s="50" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="47" t="s">
         <v>7</v>
@@ -1713,10 +1716,10 @@
         <v>8</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F20" s="50" t="s">
         <v>10</v>
@@ -1724,27 +1727,27 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="48" t="s">
         <v>33</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>34</v>
       </c>
       <c r="E21" s="49">
         <v>46241</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>7</v>
@@ -1753,58 +1756,58 @@
         <v>8</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E22" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="50" t="s">
         <v>36</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="49">
         <v>46227</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>7</v>
@@ -1813,298 +1816,298 @@
         <v>16</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E25" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E26" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E27" s="6">
         <v>46125</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E28" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="E31" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E32" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="E34" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="E36" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E37" s="6">
         <v>46161</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E38" s="6">
         <v>46147</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E39" s="6">
         <v>46122</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>7</v>
@@ -2113,433 +2116,433 @@
         <v>8</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="E42" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" s="9">
         <v>46059</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" s="9">
         <v>46181</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E45" s="9">
         <v>46227</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="E46" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" s="15" t="s">
         <v>67</v>
-      </c>
-      <c r="E46" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E47" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E48" s="9">
         <v>46161</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E49" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E50" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E51" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E52" s="9">
         <v>46181</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E53" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="E54" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="54" t="s">
         <v>92</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="E54" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" s="54" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E55" s="55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B56" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E56" s="56" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F56" s="45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="42" t="s">
+      <c r="E57" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="43" t="s">
+      <c r="F57" s="45" t="s">
         <v>82</v>
-      </c>
-      <c r="E57" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B58" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" s="43" t="s">
+      <c r="F58" s="45" t="s">
         <v>86</v>
-      </c>
-      <c r="E58" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B59" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>146</v>
+        <v>87</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>141</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F59" s="45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B60" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="42" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" s="45" t="s">
         <v>38</v>
-      </c>
-      <c r="E60" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61" s="45" t="s">
         <v>53</v>
-      </c>
-      <c r="D61" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="E61" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1773,7 +1773,7 @@
         <v>32</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="D23" s="48" t="s">
         <v>35</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="141">
   <si>
     <t>Allocation</t>
   </si>
@@ -56,9 +56,6 @@
     <t>BISEK</t>
   </si>
   <si>
-    <t>UAT DONE, Circular pending</t>
-  </si>
-  <si>
     <t>Mazhar School</t>
   </si>
   <si>
@@ -113,12 +110,6 @@
     <t>Bhawan</t>
   </si>
   <si>
-    <t>LESCO</t>
-  </si>
-  <si>
-    <t>API Shared with Paysys, Effort approved, connectivity Done and develpoment under process. Branch mapping doned, UAT done. Reports develpoed,Production connectivity done, Circular Pending at CM Ops end</t>
-  </si>
-  <si>
     <t>Payment</t>
   </si>
   <si>
@@ -368,9 +359,6 @@
     <t>IS issue. UAT DONE for UBCS, RAAST, IBFT, CMC approved,Live</t>
   </si>
   <si>
-    <t>FESCO</t>
-  </si>
-  <si>
     <t>UGDCL</t>
   </si>
   <si>
@@ -414,18 +402,6 @@
   </si>
   <si>
     <t>PASSPORT FEE MIS reporting and QR</t>
-  </si>
-  <si>
-    <t>WASA Faisalabad (Offline Biller)</t>
-  </si>
-  <si>
-    <t>UAT has been done, circular pending.</t>
-  </si>
-  <si>
-    <t>Wasa Lahore (API)</t>
-  </si>
-  <si>
-    <t>UAT DONE, Branch mapping and Mis reports pending at crpl.</t>
   </si>
   <si>
     <t>Under development</t>
@@ -680,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -732,9 +708,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1037,8 +1010,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F61" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F57" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F57"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1314,14 +1287,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1358,11 +1331,11 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="56" t="s">
-        <v>140</v>
+      <c r="E2" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,13 +1349,13 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>140</v>
+        <v>10</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1393,16 +1366,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1413,16 +1386,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1433,16 +1406,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>140</v>
+        <v>125</v>
+      </c>
+      <c r="E6" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1453,16 +1426,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1476,13 +1449,13 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1493,16 +1466,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E9" s="3">
         <v>46218</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,19 +1483,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1533,16 +1506,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="56" t="s">
-        <v>140</v>
+        <v>120</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,16 +1526,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="9">
         <v>46218</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1573,16 +1546,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="56" t="s">
-        <v>140</v>
+        <v>124</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,19 +1566,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="9">
         <v>46220</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="59" customFormat="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="56" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>6</v>
       </c>
@@ -1613,16 +1586,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>140</v>
+      <c r="E15" s="55" t="s">
+        <v>132</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1633,16 +1606,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="56" t="s">
-        <v>140</v>
+        <v>111</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1653,553 +1626,553 @@
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" s="9">
         <v>46176</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="56" t="s">
-        <v>140</v>
+        <v>30</v>
+      </c>
+      <c r="E18" s="49">
+        <v>46241</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="56" t="s">
-        <v>140</v>
+        <v>32</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="C20" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="49">
+        <v>46227</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" s="50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
+      <c r="C21" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="49">
-        <v>46241</v>
-      </c>
-      <c r="F21" s="50" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="6">
+        <v>46125</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
+      <c r="C24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="49">
-        <v>46227</v>
-      </c>
-      <c r="F24" s="50" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>16</v>
+      <c r="C25" s="40" t="s">
+        <v>62</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="56" t="s">
-        <v>140</v>
+        <v>122</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>41</v>
+      <c r="A26" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="6">
-        <v>46125</v>
+        <v>68</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>65</v>
+      <c r="A29" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>49</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="56" t="s">
-        <v>140</v>
+        <v>100</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>138</v>
+      <c r="A30" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="56" t="s">
-        <v>140</v>
+        <v>40</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>148</v>
+      <c r="E32" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>106</v>
+        <v>38</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="6">
+        <v>46161</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="56" t="s">
-        <v>140</v>
+        <v>45</v>
+      </c>
+      <c r="E34" s="6">
+        <v>46147</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="56" t="s">
-        <v>140</v>
+        <v>47</v>
+      </c>
+      <c r="E35" s="6">
+        <v>46122</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="A36" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>45</v>
+      <c r="D36" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="6">
-        <v>46161</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>47</v>
+      <c r="A37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="6">
-        <v>46147</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>49</v>
+      <c r="A38" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="6">
-        <v>46122</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>51</v>
+      <c r="A39" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="9">
+        <v>46059</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="56" t="s">
-        <v>140</v>
+        <v>56</v>
+      </c>
+      <c r="E40" s="9">
+        <v>46181</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="56" t="s">
-        <v>140</v>
+        <v>106</v>
+      </c>
+      <c r="E41" s="9">
+        <v>46227</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" s="56" t="s">
-        <v>140</v>
+        <v>63</v>
+      </c>
+      <c r="E42" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="9">
-        <v>46059</v>
+        <v>105</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="9">
-        <v>46181</v>
+        <v>46161</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>60</v>
@@ -2207,342 +2180,262 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="9">
-        <v>46227</v>
+        <v>134</v>
+      </c>
+      <c r="E45" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E46" s="56" t="s">
-        <v>140</v>
+        <v>70</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="56" t="s">
-        <v>140</v>
+        <v>73</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E48" s="9">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>70</v>
+      <c r="A49" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="7" t="s">
+      <c r="A50" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="F51" s="51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="C52" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" s="45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F51" s="15" t="s">
+      <c r="C53" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" s="43" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="9">
-        <v>46181</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="E53" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>120</v>
+      <c r="E53" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="E54" s="55" t="s">
+      <c r="A54" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F55" s="45" t="s">
         <v>85</v>
-      </c>
-      <c r="F54" s="54" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="D55" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="E55" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="F55" s="54" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B56" s="42" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="56" t="s">
-        <v>140</v>
+        <v>34</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F56" s="45" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B57" s="42" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="44" t="s">
-        <v>81</v>
+        <v>104</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>132</v>
       </c>
       <c r="F57" s="45" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="D58" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="D59" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="E59" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F60" s="45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B61" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D61" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="E61" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F61" s="45" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -446,10 +446,10 @@
     <t>Raast Bulk/SPHF</t>
   </si>
   <si>
-    <t>COC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Business as usual. </t>
+  </si>
+  <si>
+    <t>Cash over the counter (COC)</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1661,7 @@
         <v>122</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,7 +2041,7 @@
         <v>122</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,7 +2061,7 @@
         <v>122</v>
       </c>
       <c r="F38" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2321,7 +2321,7 @@
         <v>122</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2341,7 +2341,7 @@
         <v>122</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2361,7 +2361,7 @@
         <v>122</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,13 +2375,13 @@
         <v>122</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>122</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>122</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2541,7 +2541,7 @@
         <v>122</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="141">
   <si>
     <t>Allocation</t>
   </si>
@@ -263,12 +263,6 @@
     <t>Vendor Payments</t>
   </si>
   <si>
-    <t>Pay orders dispatched to CRPL.</t>
-  </si>
-  <si>
-    <t>31/07/2026</t>
-  </si>
-  <si>
     <t>Ayesha Khan</t>
   </si>
   <si>
@@ -450,6 +444,9 @@
   </si>
   <si>
     <t>Cash over the counter (COC)</t>
+  </si>
+  <si>
+    <t>Payments</t>
   </si>
 </sst>
 </file>
@@ -660,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -697,7 +694,6 @@
     <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1300,7 +1296,7 @@
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="38" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="37" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1325,7 +1321,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -1334,18 +1330,18 @@
       <c r="C2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>87</v>
+      <c r="E2" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -1354,18 +1350,18 @@
       <c r="C3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>86</v>
+      <c r="E3" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -1374,18 +1370,18 @@
       <c r="C4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="48" t="s">
+      <c r="E4" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -1394,18 +1390,18 @@
       <c r="C5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="48" t="s">
+      <c r="E5" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="47" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -1414,18 +1410,18 @@
       <c r="C6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>124</v>
+      <c r="D6" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
@@ -1434,18 +1430,18 @@
       <c r="C7" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="48" t="s">
+      <c r="E7" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -1454,18 +1450,18 @@
       <c r="C8" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>125</v>
+      <c r="E8" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -1474,38 +1470,38 @@
       <c r="C9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="48">
         <v>46218</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="47" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="49" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>121</v>
+        <v>105</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>119</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="49" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -1515,17 +1511,17 @@
         <v>19</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>121</v>
+        <v>107</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>119</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -1534,13 +1530,13 @@
       <c r="C12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="48">
         <v>46218</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1555,17 +1551,17 @@
         <v>19</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>94</v>
+        <v>111</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="19" t="s">
@@ -1574,18 +1570,18 @@
       <c r="C14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="48">
         <v>46220</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="47" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+    <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -1594,38 +1590,38 @@
       <c r="C15" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" s="48" t="s">
+      <c r="E15" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="47" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="51" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>121</v>
+        <v>128</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>119</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="19" t="s">
@@ -1634,34 +1630,34 @@
       <c r="C17" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="48">
         <v>46176</v>
       </c>
-      <c r="F17" s="48" t="s">
-        <v>126</v>
+      <c r="F17" s="47" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="51" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>120</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1692,13 +1688,13 @@
         <v>29</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>121</v>
+      <c r="E20" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F20" s="34" t="s">
         <v>33</v>
@@ -1735,13 +1731,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>121</v>
+        <v>86</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1755,13 +1751,13 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>121</v>
+        <v>88</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,13 +1771,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E24" s="3">
         <v>46125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,13 +1791,13 @@
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,13 +1811,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1829,19 +1825,19 @@
         <v>38</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>62</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>121</v>
+        <v>116</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1857,8 +1853,8 @@
       <c r="D28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="37" t="s">
-        <v>121</v>
+      <c r="E28" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>68</v>
@@ -1875,13 +1871,13 @@
         <v>49</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>121</v>
+        <v>90</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1895,13 +1891,13 @@
         <v>49</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>121</v>
+        <v>130</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1912,16 +1908,16 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="37" t="s">
-        <v>121</v>
+      <c r="E31" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1932,16 +1928,16 @@
         <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="37" t="s">
-        <v>121</v>
+      <c r="E32" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,8 +1953,8 @@
       <c r="D33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="37" t="s">
-        <v>121</v>
+      <c r="E33" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>42</v>
@@ -1975,7 +1971,7 @@
         <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E34" s="3">
         <v>46161</v>
@@ -2025,48 +2021,48 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="43" t="s">
-        <v>140</v>
+      <c r="C37" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="43" t="s">
-        <v>140</v>
+      <c r="B38" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
@@ -2077,16 +2073,16 @@
       <c r="D39" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="37" t="s">
-        <v>121</v>
+      <c r="E39" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>28</v>
@@ -2097,16 +2093,16 @@
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="37" t="s">
-        <v>121</v>
+      <c r="E40" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
@@ -2117,8 +2113,8 @@
       <c r="D41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="37" t="s">
-        <v>121</v>
+      <c r="E41" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>54</v>
@@ -2126,7 +2122,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>7</v>
@@ -2141,12 +2137,12 @@
         <v>46059</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>43</v>
@@ -2166,7 +2162,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>7</v>
@@ -2175,7 +2171,7 @@
         <v>19</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E44" s="6">
         <v>46227</v>
@@ -2186,7 +2182,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>43</v>
@@ -2195,10 +2191,10 @@
         <v>62</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>121</v>
+        <v>133</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>63</v>
@@ -2206,7 +2202,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>28</v>
@@ -2226,7 +2222,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>28</v>
@@ -2235,10 +2231,10 @@
         <v>8</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E47" s="37" t="s">
         <v>121</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>66</v>
@@ -2246,7 +2242,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>28</v>
@@ -2257,16 +2253,16 @@
       <c r="D48" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="37" t="s">
-        <v>121</v>
+      <c r="E48" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>7</v>
@@ -2277,8 +2273,8 @@
       <c r="D49" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="37" t="s">
-        <v>121</v>
+      <c r="E49" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>73</v>
@@ -2286,7 +2282,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>28</v>
@@ -2301,147 +2297,147 @@
         <v>46181</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>122</v>
+        <v>135</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>120</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>122</v>
+        <v>137</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>120</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>122</v>
+        <v>139</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>120</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>121</v>
+        <v>102</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="E56" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="F56" s="35" t="s">
         <v>82</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="53" t="s">
-        <v>122</v>
+        <v>134</v>
+      </c>
+      <c r="E57" s="52" t="s">
+        <v>120</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,8 +2453,8 @@
       <c r="D58" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E58" s="37" t="s">
-        <v>121</v>
+      <c r="E58" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>71</v>
@@ -2477,8 +2473,8 @@
       <c r="D59" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E59" s="54" t="s">
-        <v>121</v>
+      <c r="E59" s="53" t="s">
+        <v>119</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>77</v>
@@ -2497,8 +2493,8 @@
       <c r="D60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="37" t="s">
-        <v>121</v>
+      <c r="E60" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>35</v>
@@ -2515,10 +2511,10 @@
         <v>49</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>119</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>50</v>
@@ -2529,19 +2525,19 @@
         <v>74</v>
       </c>
       <c r="B62" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C62" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E62" s="54" t="s">
-        <v>122</v>
+      <c r="E62" s="53" t="s">
+        <v>120</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="141">
   <si>
     <t>Allocation</t>
   </si>
@@ -657,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -703,7 +703,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1321,7 +1320,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -1330,18 +1329,18 @@
       <c r="C2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="46" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -1350,18 +1349,18 @@
       <c r="C3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="47" t="s">
+      <c r="E3" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="46" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -1370,18 +1369,18 @@
       <c r="C4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="47" t="s">
+      <c r="E4" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="46" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -1390,18 +1389,18 @@
       <c r="C5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="47" t="s">
+      <c r="E5" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="46" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -1410,18 +1409,18 @@
       <c r="C6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="47" t="s">
+      <c r="E6" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="46" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
@@ -1430,18 +1429,18 @@
       <c r="C7" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="47" t="s">
+      <c r="E7" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="46" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -1450,18 +1449,18 @@
       <c r="C8" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="47" t="s">
+      <c r="E8" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="46" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -1470,18 +1469,18 @@
       <c r="C9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="47">
         <v>46218</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="46" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="48" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
@@ -1493,7 +1492,7 @@
       <c r="D10" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="45" t="s">
         <v>119</v>
       </c>
       <c r="F10" s="22" t="s">
@@ -1501,7 +1500,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -1513,7 +1512,7 @@
       <c r="D11" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="45" t="s">
         <v>119</v>
       </c>
       <c r="F11" s="22" t="s">
@@ -1521,7 +1520,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -1530,13 +1529,13 @@
       <c r="C12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="47">
         <v>46218</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1553,15 +1552,15 @@
       <c r="D13" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="50" t="s">
+      <c r="E13" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="49" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="19" t="s">
@@ -1570,18 +1569,18 @@
       <c r="C14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>46220</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="46" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -1590,21 +1589,21 @@
       <c r="C15" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="47" t="s">
+      <c r="E15" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="46" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="19" t="s">
@@ -1613,7 +1612,7 @@
       <c r="D16" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="45" t="s">
         <v>119</v>
       </c>
       <c r="F16" s="22" t="s">
@@ -1621,7 +1620,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="19" t="s">
@@ -1630,21 +1629,21 @@
       <c r="C17" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <v>46176</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="46" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
@@ -1653,9 +1652,7 @@
       <c r="D18" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="46" t="s">
-        <v>120</v>
-      </c>
+      <c r="E18" s="45"/>
       <c r="F18" s="22" t="s">
         <v>138</v>
       </c>
@@ -2033,9 +2030,7 @@
       <c r="D37" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="43" t="s">
-        <v>120</v>
-      </c>
+      <c r="E37" s="45"/>
       <c r="F37" s="42" t="s">
         <v>138</v>
       </c>
@@ -2053,9 +2048,7 @@
       <c r="D38" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="43" t="s">
-        <v>120</v>
-      </c>
+      <c r="E38" s="45"/>
       <c r="F38" s="42" t="s">
         <v>138</v>
       </c>
@@ -2313,9 +2306,7 @@
       <c r="D51" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E51" s="36" t="s">
-        <v>120</v>
-      </c>
+      <c r="E51" s="36"/>
       <c r="F51" s="10" t="s">
         <v>138</v>
       </c>
@@ -2333,9 +2324,7 @@
       <c r="D52" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="36" t="s">
-        <v>120</v>
-      </c>
+      <c r="E52" s="36"/>
       <c r="F52" s="10" t="s">
         <v>138</v>
       </c>
@@ -2353,9 +2342,7 @@
       <c r="D53" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="36" t="s">
-        <v>120</v>
-      </c>
+      <c r="E53" s="36"/>
       <c r="F53" s="10" t="s">
         <v>138</v>
       </c>
@@ -2373,9 +2360,7 @@
       <c r="D54" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E54" s="36" t="s">
-        <v>120</v>
-      </c>
+      <c r="E54" s="36"/>
       <c r="F54" s="10" t="s">
         <v>138</v>
       </c>
@@ -2413,9 +2398,7 @@
       <c r="D56" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="52" t="s">
-        <v>120</v>
-      </c>
+      <c r="E56" s="51"/>
       <c r="F56" s="35" t="s">
         <v>82</v>
       </c>
@@ -2433,9 +2416,7 @@
       <c r="D57" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E57" s="52" t="s">
-        <v>120</v>
-      </c>
+      <c r="E57" s="51"/>
       <c r="F57" s="35" t="s">
         <v>138</v>
       </c>
@@ -2473,7 +2454,7 @@
       <c r="D59" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E59" s="53" t="s">
+      <c r="E59" s="52" t="s">
         <v>119</v>
       </c>
       <c r="F59" s="29" t="s">
@@ -2533,9 +2514,7 @@
       <c r="D62" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="53" t="s">
-        <v>120</v>
-      </c>
+      <c r="E62" s="52"/>
       <c r="F62" s="29" t="s">
         <v>138</v>
       </c>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="141">
   <si>
     <t>Allocation</t>
   </si>
@@ -1652,7 +1652,9 @@
       <c r="D18" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="45"/>
+      <c r="E18" s="45" t="s">
+        <v>120</v>
+      </c>
       <c r="F18" s="22" t="s">
         <v>138</v>
       </c>
@@ -2030,7 +2032,9 @@
       <c r="D37" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="45"/>
+      <c r="E37" s="45" t="s">
+        <v>120</v>
+      </c>
       <c r="F37" s="42" t="s">
         <v>138</v>
       </c>
@@ -2048,7 +2052,9 @@
       <c r="D38" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="45"/>
+      <c r="E38" s="45" t="s">
+        <v>120</v>
+      </c>
       <c r="F38" s="42" t="s">
         <v>138</v>
       </c>
@@ -2306,7 +2312,9 @@
       <c r="D51" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E51" s="36"/>
+      <c r="E51" s="36" t="s">
+        <v>120</v>
+      </c>
       <c r="F51" s="10" t="s">
         <v>138</v>
       </c>
@@ -2324,7 +2332,9 @@
       <c r="D52" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="36"/>
+      <c r="E52" s="36" t="s">
+        <v>120</v>
+      </c>
       <c r="F52" s="10" t="s">
         <v>138</v>
       </c>
@@ -2342,7 +2352,9 @@
       <c r="D53" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="36" t="s">
+        <v>120</v>
+      </c>
       <c r="F53" s="10" t="s">
         <v>138</v>
       </c>
@@ -2360,7 +2372,9 @@
       <c r="D54" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E54" s="36"/>
+      <c r="E54" s="36" t="s">
+        <v>120</v>
+      </c>
       <c r="F54" s="10" t="s">
         <v>138</v>
       </c>
@@ -2398,7 +2412,9 @@
       <c r="D56" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="51"/>
+      <c r="E56" s="51" t="s">
+        <v>120</v>
+      </c>
       <c r="F56" s="35" t="s">
         <v>82</v>
       </c>
@@ -2416,7 +2432,9 @@
       <c r="D57" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E57" s="51"/>
+      <c r="E57" s="51" t="s">
+        <v>120</v>
+      </c>
       <c r="F57" s="35" t="s">
         <v>138</v>
       </c>
@@ -2514,7 +2532,9 @@
       <c r="D62" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E62" s="52"/>
+      <c r="E62" s="52" t="s">
+        <v>120</v>
+      </c>
       <c r="F62" s="29" t="s">
         <v>138</v>
       </c>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="137">
   <si>
     <t>Allocation</t>
   </si>
@@ -212,9 +212,6 @@
     <t>Tokinization on SmartPAY</t>
   </si>
   <si>
-    <t>Under Development</t>
-  </si>
-  <si>
     <t>Requirement shared with CRPL, SOW finalizaed, FSD finalized, under development</t>
   </si>
   <si>
@@ -372,15 +369,6 @@
   </si>
   <si>
     <t>SOW finalized, FSD received, Under UAT,Under Is review. For CMC approval</t>
-  </si>
-  <si>
-    <t>VM Transafer</t>
-  </si>
-  <si>
-    <t>AT IT end.</t>
-  </si>
-  <si>
-    <t>Both</t>
   </si>
   <si>
     <t>TBD</t>
@@ -1288,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -1333,10 +1321,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1353,10 +1341,10 @@
         <v>10</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1373,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>12</v>
@@ -1393,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>14</v>
@@ -1410,13 +1398,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1427,13 +1415,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F7" s="46" t="s">
         <v>17</v>
@@ -1453,10 +1441,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="46" t="s">
         <v>119</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,19 +1472,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>105</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,13 +1498,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1550,13 +1538,13 @@
         <v>19</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,13 +1578,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="46" t="s">
         <v>64</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1610,13 +1598,13 @@
         <v>49</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1636,7 +1624,7 @@
         <v>46176</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1647,16 +1635,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1687,13 +1675,13 @@
         <v>29</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>119</v>
+      <c r="E20" s="36">
+        <v>46261</v>
       </c>
       <c r="F20" s="34" t="s">
         <v>33</v>
@@ -1730,13 +1718,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>86</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1750,13 +1738,13 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1770,13 +1758,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3">
         <v>46125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1790,13 +1778,13 @@
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1810,53 +1798,53 @@
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>110</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>116</v>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>67</v>
+      <c r="D28" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>68</v>
+        <v>115</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1870,33 +1858,33 @@
         <v>49</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>130</v>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>93</v>
+        <v>115</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,16 +1895,16 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>119</v>
+        <v>40</v>
+      </c>
+      <c r="E31" s="36">
+        <v>46276</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1927,16 +1915,16 @@
         <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1947,16 +1935,16 @@
         <v>28</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>119</v>
+        <v>88</v>
+      </c>
+      <c r="E33" s="3">
+        <v>46161</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1970,13 +1958,13 @@
         <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="E34" s="3">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1990,33 +1978,33 @@
         <v>19</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E35" s="3">
-        <v>46147</v>
+        <v>46122</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="3">
-        <v>46122</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>48</v>
+      <c r="C36" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2024,56 +2012,56 @@
         <v>38</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>138</v>
+      <c r="A38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>96</v>
@@ -2081,462 +2069,442 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>119</v>
+        <v>55</v>
+      </c>
+      <c r="E41" s="6">
+        <v>46059</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E42" s="6">
-        <v>46059</v>
+        <v>46181</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="E43" s="6">
-        <v>46181</v>
+        <v>46227</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="6">
-        <v>46227</v>
+        <v>129</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>115</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>119</v>
+        <v>59</v>
+      </c>
+      <c r="E45" s="6">
+        <v>46161</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="6">
-        <v>46161</v>
+        <v>117</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>115</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E47" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>119</v>
+        <v>61</v>
+      </c>
+      <c r="E49" s="6">
+        <v>46181</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="6">
-        <v>46181</v>
+        <v>131</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>116</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="C52" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>139</v>
+      <c r="A54" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>101</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>138</v>
+        <v>115</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>103</v>
+      <c r="C55" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F57" s="35" t="s">
-        <v>138</v>
+      <c r="A57" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="27" t="s">
-        <v>7</v>
-      </c>
       <c r="C58" s="27" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>119</v>
+        <v>75</v>
+      </c>
+      <c r="E58" s="52" t="s">
+        <v>115</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="52" t="s">
-        <v>119</v>
+        <v>34</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>115</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>119</v>
+        <v>77</v>
+      </c>
+      <c r="E61" s="52" t="s">
+        <v>116</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="F62" s="29" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -2035,7 +2035,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>51</v>
@@ -2155,7 +2155,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>129</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -230,9 +230,6 @@
     <t>Initial meeting done with vendor and customer, SOW in process</t>
   </si>
   <si>
-    <t>Optimization</t>
-  </si>
-  <si>
     <t>PTCL Advance Payment</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>Payments</t>
+  </si>
+  <si>
+    <t>IBFT &amp; UBPS Workflow</t>
   </si>
 </sst>
 </file>
@@ -1321,10 +1321,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>10</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>12</v>
@@ -1381,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>14</v>
@@ -1398,13 +1398,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1421,7 +1421,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F7" s="46" t="s">
         <v>17</v>
@@ -1441,10 +1441,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1472,19 +1472,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>104</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,13 +1498,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1538,13 +1538,13 @@
         <v>19</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F15" s="46" t="s">
         <v>64</v>
@@ -1598,13 +1598,13 @@
         <v>49</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,7 +1624,7 @@
         <v>46176</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,16 +1635,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,13 +1718,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>85</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1738,13 +1738,13 @@
         <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,13 +1758,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3">
         <v>46125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1778,13 +1778,13 @@
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1798,13 +1798,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,7 +1821,7 @@
         <v>66</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>67</v>
@@ -1838,13 +1838,13 @@
         <v>49</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1858,13 +1858,13 @@
         <v>49</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,16 +1875,16 @@
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,7 +1904,7 @@
         <v>46276</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1921,7 +1921,7 @@
         <v>41</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>42</v>
@@ -1938,7 +1938,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="3">
         <v>46161</v>
@@ -1995,16 +1995,16 @@
         <v>28</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2015,41 +2015,41 @@
         <v>7</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>28</v>
@@ -2061,15 +2061,15 @@
         <v>52</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
@@ -2081,7 +2081,7 @@
         <v>53</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>54</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
@@ -2104,12 +2104,12 @@
         <v>46059</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>43</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>7</v>
@@ -2138,7 +2138,7 @@
         <v>19</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E43" s="6">
         <v>46227</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>43</v>
@@ -2158,10 +2158,10 @@
         <v>8</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>62</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>28</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>28</v>
@@ -2198,10 +2198,10 @@
         <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>65</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>28</v>
@@ -2218,18 +2218,18 @@
         <v>49</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>7</v>
@@ -2238,18 +2238,18 @@
         <v>49</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>28</v>
@@ -2264,152 +2264,152 @@
         <v>46181</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D54" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="C55" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C55" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="35" t="s">
+      <c r="E55" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F55" s="35" t="s">
         <v>80</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="F55" s="35" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>7</v>
@@ -2418,38 +2418,38 @@
         <v>8</v>
       </c>
       <c r="D57" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" s="29" t="s">
         <v>69</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F57" s="29" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="27" t="s">
         <v>73</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>74</v>
       </c>
       <c r="C58" s="27" t="s">
         <v>49</v>
       </c>
       <c r="D58" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" s="29" t="s">
         <v>75</v>
-      </c>
-      <c r="E58" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="F58" s="29" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>29</v>
@@ -2461,7 +2461,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>35</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>7</v>
@@ -2478,10 +2478,10 @@
         <v>49</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>50</v>
@@ -2489,22 +2489,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E61" s="52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
